--- a/Denver_Nuggets_2025-26_stats.xlsx
+++ b/Denver_Nuggets_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,6 +1148,63 @@
       </c>
       <c r="Q12" t="n">
         <v>18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" t="n">
+        <v>23</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>27</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1161,7 +1218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1876,6 +1933,63 @@
       </c>
       <c r="Q12" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>11</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1889,7 +2003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2604,6 +2718,63 @@
       </c>
       <c r="Q12" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2617,7 +2788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3332,6 +3503,63 @@
       </c>
       <c r="Q12" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3367,7 +3595,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.81818181818182</v>
+        <v>28.66666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -3377,7 +3605,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>22.09090909090909</v>
       </c>
     </row>
     <row r="4">
@@ -3387,27 +3615,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.6</v>
+        <v>19.90909090909091</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.36363636363636</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>11.36363636363636</v>
       </c>
     </row>
     <row r="7">
@@ -3417,7 +3645,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.909090909090908</v>
+        <v>8.666666666666666</v>
       </c>
     </row>
     <row r="8">
@@ -3437,7 +3665,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.636363636363637</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -3447,7 +3675,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="11">
@@ -3457,7 +3685,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.125</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -3477,7 +3705,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.857142857142857</v>
+        <v>1.875</v>
       </c>
     </row>
     <row r="14">
@@ -3543,7 +3771,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.90909090909091</v>
+        <v>10.91666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -3553,7 +3781,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7</v>
+        <v>6.272727272727272</v>
       </c>
     </row>
     <row r="4">
@@ -3583,7 +3811,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.636363636363636</v>
+        <v>1.583333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3593,7 +3821,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.6</v>
+        <v>1.545454545454545</v>
       </c>
     </row>
     <row r="8">
@@ -3603,7 +3831,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.454545454545455</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3613,7 +3841,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.363636363636364</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -3623,7 +3851,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.181818181818182</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="11">
@@ -3639,7 +3867,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Julian Strawther</t>
+          <t>Spencer Jones</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -3649,11 +3877,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Julian Strawther</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="14">
@@ -3719,7 +3947,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13.09090909090909</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -3729,7 +3957,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5</v>
+        <v>5.909090909090909</v>
       </c>
     </row>
     <row r="4">
@@ -3739,7 +3967,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>5.090909090909091</v>
       </c>
     </row>
     <row r="5">
@@ -3749,23 +3977,23 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.818181818181818</v>
+        <v>4.916666666666667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.363636363636363</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -3779,7 +4007,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.727272727272727</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="9">
@@ -3809,7 +4037,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.818181818181818</v>
+        <v>1.916666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -3819,7 +4047,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.625</v>
+        <v>1.555555555555556</v>
       </c>
     </row>
     <row r="13">
@@ -3849,7 +4077,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16">
@@ -3895,27 +4123,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.545454545454545</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.4</v>
+        <v>2.454545454545455</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.3</v>
+        <v>2.272727272727273</v>
       </c>
     </row>
     <row r="5">
@@ -3925,7 +4153,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.818181818181818</v>
+        <v>1.916666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -3935,7 +4163,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7">
@@ -3975,7 +4203,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -3995,7 +4223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13">
@@ -4005,7 +4233,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.25</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="14">
@@ -4015,7 +4243,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -4049,7 +4277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4310,6 +4538,27 @@
         <v>246</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>123</v>
+      </c>
+      <c r="D13" t="n">
+        <v>112</v>
+      </c>
+      <c r="E13" t="n">
+        <v>235</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
